--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFF7061-84CC-42D3-B773-A146655BC526}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71124D72-22B0-4F3F-A469-11C3F6EF4798}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="1140" windowWidth="13635" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="163">
   <si>
     <t>index</t>
   </si>
@@ -493,9 +493,6 @@
   </si>
   <si>
     <t>d_an_ca</t>
-  </si>
-  <si>
-    <t>d_an_cv_1;d_an_cv_2;d_an_cv_3;d_an_cv_4;</t>
   </si>
   <si>
     <t>d_f_mp1</t>
@@ -1252,7 +1249,7 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>139</v>
@@ -1373,13 +1370,13 @@
         <v>13</v>
       </c>
       <c r="F16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>151</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>136</v>
@@ -1471,13 +1468,13 @@
         <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>151</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>136</v>
@@ -1497,13 +1494,13 @@
         <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>151</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>136</v>
@@ -1512,7 +1509,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>53</v>
       </c>
@@ -1522,9 +1519,7 @@
       <c r="D22" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>156</v>
-      </c>
+      <c r="F22" s="8"/>
       <c r="G22" s="5" t="s">
         <v>146</v>
       </c>
@@ -1555,7 +1550,7 @@
         <v>151</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>136</v>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71124D72-22B0-4F3F-A469-11C3F6EF4798}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DE2C02-0444-4D35-A06C-6DBBEC2DC49B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="1140" windowWidth="13635" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="162">
   <si>
     <t>index</t>
   </si>
@@ -501,19 +501,16 @@
     <t>d_an_cv_6</t>
   </si>
   <si>
-    <t>d_fa_m3_dm</t>
-  </si>
-  <si>
     <t>a_packyears</t>
   </si>
   <si>
-    <t>recode(2= 0; 11= 1;12=1;13=1;14=1;ELSE=NA;)</t>
-  </si>
-  <si>
     <t>recode(1= 1; 2 = 0;ELSE=NA;)</t>
   </si>
   <si>
     <t>recode(1= 1; 2 = 0;ELSE=NA)</t>
+  </si>
+  <si>
+    <t>a_diab</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1246,7 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>139</v>
@@ -1376,7 +1373,7 @@
         <v>151</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>136</v>
@@ -1468,19 +1465,19 @@
         <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>158</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>136</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
@@ -1500,7 +1497,7 @@
         <v>151</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>136</v>
@@ -1550,7 +1547,7 @@
         <v>151</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>136</v>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DE2C02-0444-4D35-A06C-6DBBEC2DC49B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33571666-D78F-4584-8EF8-E53FBE3B1987}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="1140" windowWidth="13635" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="163">
   <si>
     <t>index</t>
   </si>
@@ -511,6 +511,9 @@
   </si>
   <si>
     <t>a_diab</t>
+  </si>
+  <si>
+    <t>undetermined</t>
   </si>
 </sst>
 </file>
@@ -1173,17 +1176,18 @@
       <c r="D8" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>147</v>
+      <c r="G8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1222,17 +1226,18 @@
       <c r="D10" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>147</v>
+      <c r="G10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1271,17 +1276,18 @@
       <c r="D12" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>147</v>
+      <c r="G12" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1320,17 +1326,18 @@
       <c r="D14" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>147</v>
+      <c r="G14" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1343,17 +1350,18 @@
       <c r="D15" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>147</v>
+      <c r="G15" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1517,17 +1525,18 @@
         <v>13</v>
       </c>
       <c r="F22" s="8"/>
-      <c r="G22" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>147</v>
+      <c r="G22" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
@@ -1566,17 +1575,18 @@
       <c r="D24" t="s">
         <v>13</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>147</v>
+      <c r="G24" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
@@ -1589,17 +1599,18 @@
       <c r="D25" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>147</v>
+      <c r="G25" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
@@ -1612,17 +1623,18 @@
       <c r="D26" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>147</v>
+      <c r="G26" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1704,17 +1716,18 @@
       <c r="D30" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>147</v>
+      <c r="G30" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
@@ -1727,17 +1740,18 @@
       <c r="D31" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>147</v>
+      <c r="G31" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
@@ -2303,18 +2317,18 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>147</v>
+      <c r="G54" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2329,18 +2343,18 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="I55" s="2"/>
-      <c r="J55" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>147</v>
+      <c r="G55" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
@@ -2355,18 +2369,18 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
-      <c r="G56" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="H56" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="I56" s="2"/>
-      <c r="J56" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="K56" s="11" t="s">
-        <v>147</v>
+      <c r="G56" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2381,18 +2395,18 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
-      <c r="G57" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="I57" s="2"/>
-      <c r="J57" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>147</v>
+      <c r="G57" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="58" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2407,18 +2421,18 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
-      <c r="G58" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="H58" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="I58" s="2"/>
-      <c r="J58" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>147</v>
+      <c r="G58" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2433,18 +2447,18 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>147</v>
+      <c r="G59" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2459,18 +2473,18 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
-      <c r="G60" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>147</v>
+      <c r="G60" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="61" spans="2:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2485,18 +2499,17 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
-      <c r="G61" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>147</v>
+      <c r="G61" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33571666-D78F-4584-8EF8-E53FBE3B1987}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EC473B-3430-410D-9AFB-D26A3C9D6977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1245" yWindow="1140" windowWidth="13635" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="162">
   <si>
     <t>index</t>
   </si>
@@ -427,9 +427,6 @@
   </si>
   <si>
     <t>Age at end of follow-up [years]</t>
-  </si>
-  <si>
-    <t>id</t>
   </si>
   <si>
     <t>id_creation</t>
@@ -623,7 +620,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -639,9 +636,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -679,9 +676,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -714,26 +711,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -766,26 +746,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -960,7 +923,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="59.140625" bestFit="1" customWidth="1"/>
@@ -1020,20 +983,20 @@
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1047,19 +1010,19 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="H3" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1073,19 +1036,19 @@
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J4" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1099,19 +1062,19 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J5" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1125,19 +1088,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K6" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1151,19 +1114,19 @@
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J7" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1177,17 +1140,17 @@
         <v>13</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1201,19 +1164,19 @@
         <v>13</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1227,17 +1190,17 @@
         <v>18</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1251,19 +1214,19 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J11" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1277,17 +1240,17 @@
         <v>18</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1301,19 +1264,19 @@
         <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J13" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1327,17 +1290,17 @@
         <v>13</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1351,17 +1314,17 @@
         <v>13</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1375,19 +1338,19 @@
         <v>13</v>
       </c>
       <c r="F16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -1401,16 +1364,16 @@
         <v>13</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
@@ -1424,19 +1387,19 @@
         <v>13</v>
       </c>
       <c r="F18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J18" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="K18" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
@@ -1450,16 +1413,16 @@
         <v>18</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
@@ -1473,19 +1436,19 @@
         <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J20" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K20" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
@@ -1499,19 +1462,19 @@
         <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
@@ -1526,17 +1489,17 @@
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
@@ -1550,19 +1513,19 @@
         <v>13</v>
       </c>
       <c r="F23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
@@ -1576,17 +1539,17 @@
         <v>13</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
@@ -1600,17 +1563,17 @@
         <v>13</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
@@ -1624,17 +1587,17 @@
         <v>13</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1648,16 +1611,16 @@
         <v>13</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
@@ -1671,16 +1634,16 @@
         <v>13</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
@@ -1694,16 +1657,16 @@
         <v>13</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
@@ -1717,17 +1680,17 @@
         <v>13</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
@@ -1741,17 +1704,17 @@
         <v>13</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I31" s="7"/>
       <c r="J31" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
@@ -1765,16 +1728,16 @@
         <v>13</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
@@ -1788,16 +1751,16 @@
         <v>13</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
@@ -1811,16 +1774,16 @@
         <v>13</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
@@ -1834,16 +1797,16 @@
         <v>13</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
@@ -1857,16 +1820,16 @@
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
@@ -1880,16 +1843,16 @@
         <v>18</v>
       </c>
       <c r="G37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="2:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1905,17 +1868,17 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="2:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1931,17 +1894,17 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I39" s="2"/>
       <c r="J39" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="2:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1957,17 +1920,17 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I40" s="2"/>
       <c r="J40" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="2:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1983,17 +1946,17 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I41" s="2"/>
       <c r="J41" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="2:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2009,17 +1972,17 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I42" s="2"/>
       <c r="J42" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="2:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2035,17 +1998,17 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="2:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2059,16 +2022,16 @@
         <v>13</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
@@ -2084,17 +2047,17 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
@@ -2110,17 +2073,17 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -2136,17 +2099,17 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2162,17 +2125,17 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2188,17 +2151,17 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
@@ -2214,17 +2177,17 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
@@ -2240,17 +2203,17 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2266,17 +2229,17 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2292,17 +2255,17 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
@@ -2318,17 +2281,17 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I54" s="7"/>
       <c r="J54" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2344,17 +2307,17 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
@@ -2370,17 +2333,17 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2396,17 +2359,17 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2422,17 +2385,17 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I58" s="7"/>
       <c r="J58" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2448,17 +2411,17 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2474,17 +2437,17 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="2:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2500,16 +2463,16 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EC473B-3430-410D-9AFB-D26A3C9D6977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8685A59-972F-4CEB-A8AB-E348581421EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="161">
   <si>
     <t>index</t>
   </si>
@@ -501,16 +501,13 @@
     <t>a_packyears</t>
   </si>
   <si>
-    <t>recode(1= 1; 2 = 0;ELSE=NA;)</t>
-  </si>
-  <si>
-    <t>recode(1= 1; 2 = 0;ELSE=NA)</t>
-  </si>
-  <si>
     <t>a_diab</t>
   </si>
   <si>
     <t>undetermined</t>
+  </si>
+  <si>
+    <t>recode(1= 1; 2 = 0;)</t>
   </si>
 </sst>
 </file>
@@ -1140,17 +1137,17 @@
         <v>13</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1190,17 +1187,17 @@
         <v>18</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1240,17 +1237,17 @@
         <v>18</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1290,17 +1287,17 @@
         <v>13</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1314,17 +1311,17 @@
         <v>13</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1344,7 +1341,7 @@
         <v>150</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>135</v>
@@ -1436,7 +1433,7 @@
         <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>138</v>
@@ -1468,7 +1465,7 @@
         <v>150</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>135</v>
@@ -1489,17 +1486,17 @@
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
@@ -1519,7 +1516,7 @@
         <v>150</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>135</v>
@@ -1539,17 +1536,17 @@
         <v>13</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
@@ -1563,17 +1560,17 @@
         <v>13</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
@@ -1587,17 +1584,17 @@
         <v>13</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1680,17 +1677,17 @@
         <v>13</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
@@ -1704,17 +1701,17 @@
         <v>13</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I31" s="7"/>
       <c r="J31" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
@@ -2281,17 +2278,17 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I54" s="7"/>
       <c r="J54" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2307,17 +2304,17 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
@@ -2333,17 +2330,17 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2359,17 +2356,17 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2385,17 +2382,17 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I58" s="7"/>
       <c r="J58" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2411,17 +2408,17 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="2:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -2437,17 +2434,17 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="2:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2463,16 +2460,16 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_NAKO_TRACY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8685A59-972F-4CEB-A8AB-E348581421EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E5E7B1-6DDC-451C-8ED1-710368A3D2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
